--- a/KatalonData/RADTestData/EmailNoMatch.xlsx
+++ b/KatalonData/RADTestData/EmailNoMatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="148">
   <si>
     <t>Execute</t>
   </si>
@@ -310,12 +310,181 @@
   </si>
   <si>
     <t>Mon Aug 03 15:34:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:45:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:45:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:46:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:47:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:47:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:48:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:48:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:51:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:52:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:53:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:54:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:56:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:56:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:58:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:00:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:01:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:03:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:04:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:04:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:05:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:06:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:07:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:08:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:10:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:10:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:11:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:13:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:13:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:15:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:18:52 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -682,12 +851,12 @@
   <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="34.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="34.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -712,7 +881,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -729,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -746,7 +915,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -763,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -780,7 +949,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -797,7 +966,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -814,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -831,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -848,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -865,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -882,7 +1051,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -899,7 +1068,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -916,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -933,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -950,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -967,7 +1136,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -984,7 +1153,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1001,7 +1170,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1018,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1035,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1052,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1069,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1086,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1103,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1120,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1137,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1154,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1171,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1188,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1205,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1222,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1239,7 +1408,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1256,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1284,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1301,7 +1470,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1318,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1335,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1352,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1380,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1397,7 +1566,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1414,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1431,7 +1600,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1447,8 +1616,8 @@
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B46" t="s">
-        <v>91</v>
+      <c r="B46" t="s" s="1">
+        <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1465,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1482,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1499,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1516,7 +1685,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1533,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1550,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -1567,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1584,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1601,7 +1770,7 @@
         <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1618,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1657,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -1674,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -1691,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>

--- a/KatalonData/RADTestData/EmailNoMatch.xlsx
+++ b/KatalonData/RADTestData/EmailNoMatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="148">
   <si>
     <t>Execute</t>
   </si>
@@ -310,12 +310,181 @@
   </si>
   <si>
     <t>Mon Aug 03 15:34:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:42:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:43:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:44:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:45:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:46:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:47:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:48:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:49:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:50:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:36 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -682,12 +851,12 @@
   <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="34.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="34.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -712,7 +881,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -729,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -746,7 +915,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -763,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -780,7 +949,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -797,7 +966,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -814,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -831,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -848,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -865,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -882,7 +1051,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -899,7 +1068,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -916,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -933,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -950,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -967,7 +1136,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -984,7 +1153,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1001,7 +1170,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1018,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1035,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1052,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1069,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1086,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1103,7 +1272,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1120,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1137,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1154,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1171,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1188,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1205,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1222,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1239,7 +1408,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1256,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1284,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1301,7 +1470,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1318,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1335,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1352,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1380,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1397,7 +1566,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1414,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1431,7 +1600,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1447,8 +1616,8 @@
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B46" t="s">
-        <v>91</v>
+      <c r="B46" t="s" s="1">
+        <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1465,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1482,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1499,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1516,7 +1685,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1533,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1550,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -1567,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1584,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1601,7 +1770,7 @@
         <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1618,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1657,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -1674,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -1691,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
